--- a/demo/v0.6.0/StructureDefinition-preview-model.xlsx
+++ b/demo/v0.6.0/StructureDefinition-preview-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:58:28+00:00</t>
+    <t>2026-08-27T19:49:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
